--- a/modules/07-Final-project/inicio/bbdd/bbdd-examples.xlsx
+++ b/modules/07-Final-project/inicio/bbdd/bbdd-examples.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\dev\UNIR-Full-Stack-Developer\modules\07-Final-project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\dev\UNIR-Full-Stack-Developer\modules\07-Final-project\inicio\bbdd\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{576FB358-3366-442F-9A47-E8916F290985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17348028-B632-4667-8352-E522DFE1DF4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{159F6CC9-B513-45F1-8E9B-A5D4CED763F6}"/>
+    <workbookView xWindow="-28365" yWindow="1575" windowWidth="27780" windowHeight="12270" xr2:uid="{159F6CC9-B513-45F1-8E9B-A5D4CED763F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -236,7 +236,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -264,26 +264,6 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -321,15 +301,6 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -341,26 +312,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -371,7 +322,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -381,24 +332,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -409,82 +346,73 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -493,7 +421,25 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -817,407 +763,393 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B493269-D8EC-4F49-ABA2-1C5F48301CB8}">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2.7265625" customWidth="1"/>
-    <col min="2" max="2" width="22.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.81640625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="17.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="2.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.08984375" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="2" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.453125" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="22.453125" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" s="18" t="s">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="19" t="s">
+      <c r="B2" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="20">
-        <v>1</v>
-      </c>
-      <c r="B3" s="20" t="s">
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="14">
+        <v>1</v>
+      </c>
+      <c r="B3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="43" t="s">
+      <c r="D3" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="43" t="s">
+      <c r="E3" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="20">
-        <v>2</v>
-      </c>
-      <c r="B4" s="20" t="s">
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="14">
+        <v>2</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="D4" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="43" t="s">
+      <c r="E4" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A6" s="9" t="s">
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A7" s="10" t="s">
+      <c r="G6" s="55"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="56"/>
+      <c r="K6"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="11" t="s">
+      <c r="B7" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="F7" s="29" t="s">
+      <c r="F7" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="30"/>
-      <c r="H7" s="34" t="s">
+      <c r="G7" s="40"/>
+      <c r="H7" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="I7" s="44"/>
-      <c r="J7" s="35"/>
-      <c r="K7" s="5" t="s">
+      <c r="I7" s="53"/>
+      <c r="J7" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A8" s="12">
-        <v>1</v>
-      </c>
-      <c r="B8" s="12" t="s">
+      <c r="K7"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" s="7">
+        <v>1</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="47">
-        <v>1</v>
-      </c>
-      <c r="G8" s="32" t="s">
+      <c r="F8" s="25">
+        <v>1</v>
+      </c>
+      <c r="G8" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="45">
-        <v>1</v>
-      </c>
-      <c r="I8" s="46"/>
-      <c r="J8" s="37" t="s">
+      <c r="H8" s="51">
+        <v>1</v>
+      </c>
+      <c r="I8" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K8" s="42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="12">
-        <v>2</v>
-      </c>
-      <c r="B9" s="12" t="s">
+      <c r="J8" s="23">
+        <v>1</v>
+      </c>
+      <c r="K8"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" s="7">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="48">
-        <v>2</v>
-      </c>
-      <c r="G9" s="33" t="s">
+      <c r="F9" s="25">
+        <v>1</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="51">
+        <v>2</v>
+      </c>
+      <c r="I9" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="J9" s="23">
+        <v>2</v>
+      </c>
+      <c r="K9"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A10" s="7">
+        <v>3</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L10" s="57"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" s="7">
+        <v>4</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="F12" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="49"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="49"/>
+      <c r="J12" s="49"/>
+      <c r="K12" s="50"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="F13" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" s="36"/>
+      <c r="J13" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="K13" s="38"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A14" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="26">
+        <v>1</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="27">
+        <v>2</v>
+      </c>
+      <c r="I14" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="J14" s="30">
+        <v>1</v>
+      </c>
+      <c r="K14" s="31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A15" s="11">
+        <v>1</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="11"/>
+      <c r="F15" s="26">
+        <v>2</v>
+      </c>
+      <c r="G15" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="45">
-        <v>2</v>
-      </c>
-      <c r="I9" s="46"/>
-      <c r="J9" s="36" t="s">
+      <c r="H15" s="27">
+        <v>2</v>
+      </c>
+      <c r="I15" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="J15" s="30">
+        <v>1</v>
+      </c>
+      <c r="K15" s="31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A16" s="11">
+        <v>2</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="K9" s="42">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A10" s="12">
+      <c r="C16" s="11"/>
+      <c r="F16" s="26">
         <v>3</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="G16" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="27">
+        <v>2</v>
+      </c>
+      <c r="I16" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16" s="30">
+        <v>2</v>
+      </c>
+      <c r="K16" s="31" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="11">
+        <v>3</v>
+      </c>
+      <c r="B17" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="12">
+      <c r="C17" s="11"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="46"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="47"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="44"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="18">
+        <v>1</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="22">
+        <v>2</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="18">
+        <v>2</v>
+      </c>
+      <c r="B22" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="22">
+        <v>1</v>
+      </c>
+      <c r="D22" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="F12" s="59" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" s="60"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="60"/>
-      <c r="J12" s="60"/>
-      <c r="K12" s="60"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="F13" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="G13" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H13" s="52" t="s">
-        <v>20</v>
-      </c>
-      <c r="I13" s="53"/>
-      <c r="J13" s="57" t="s">
-        <v>29</v>
-      </c>
-      <c r="K13" s="58"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="48">
-        <v>1</v>
-      </c>
-      <c r="G14" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="H14" s="49">
-        <v>2</v>
-      </c>
-      <c r="I14" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="J14" s="55">
-        <v>1</v>
-      </c>
-      <c r="K14" s="56" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="17">
-        <v>1</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="17"/>
-      <c r="F15" s="48">
-        <v>2</v>
-      </c>
-      <c r="G15" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="H15" s="49">
-        <v>2</v>
-      </c>
-      <c r="I15" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="J15" s="55">
-        <v>1</v>
-      </c>
-      <c r="K15" s="56" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="17">
-        <v>2</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="17"/>
-      <c r="F16" s="48">
-        <v>3</v>
-      </c>
-      <c r="G16" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="H16" s="49">
-        <v>2</v>
-      </c>
-      <c r="I16" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="J16" s="55">
-        <v>2</v>
-      </c>
-      <c r="K16" s="56" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="17">
-        <v>3</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" s="17"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C20" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" s="28"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="24">
-        <v>1</v>
-      </c>
-      <c r="B21" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="50">
-        <v>2</v>
-      </c>
-      <c r="D21" s="61" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="24">
-        <v>2</v>
-      </c>
-      <c r="B22" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" s="38">
-        <v>1</v>
-      </c>
-      <c r="D22" s="51" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B27" s="62"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="11">
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="F12:K12"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="F6:J6"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="F12:K12"/>
-    <mergeCell ref="F6:K6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="H7:J7"/>
     <mergeCell ref="A19:D19"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="A13:C13"/>
